--- a/sample-data/don-hang-online-shopee.xlsx
+++ b/sample-data/don-hang-online-shopee.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn Shopee" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,6 +421,9 @@
       <c r="G1" t="str">
         <v>Kenh</v>
       </c>
+      <c r="H1" t="str">
+        <v>Trang thai</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -430,19 +433,22 @@
         <v>2025-07-01 10:15:00</v>
       </c>
       <c r="C2" t="str">
-        <v>Đắc Nhân Tâm - Bìa Cứng</v>
+        <v>Mãi mãi tuổi hai mươi</v>
       </c>
       <c r="D2" t="str">
-        <v>9786045678901</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>86000</v>
+        <v>9786042392440</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2" t="str">
+        <v>135000</v>
       </c>
       <c r="G2" t="str">
-        <v>Shopee</v>
+        <v>shopee vn</v>
+      </c>
+      <c r="H2" t="str">
+        <v>giao thanh cong</v>
       </c>
     </row>
     <row r="3">
@@ -453,19 +459,22 @@
         <v>2025-07-01 11:30:00</v>
       </c>
       <c r="C3" t="str">
-        <v>Nhà Giả Kim (Tái Bản)</v>
+        <v>Đắc Nhân Tâm</v>
       </c>
       <c r="D3" t="str">
-        <v>9786045678902</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>79000</v>
+        <v>9786045678901</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>86000</v>
       </c>
       <c r="G3" t="str">
-        <v>Shopee</v>
+        <v>shopee</v>
+      </c>
+      <c r="H3" t="str">
+        <v>completed</v>
       </c>
     </row>
     <row r="4">
@@ -476,19 +485,22 @@
         <v>2025-07-02 09:20:00</v>
       </c>
       <c r="C4" t="str">
-        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu?</v>
+        <v>Nha Gia Kim</v>
       </c>
       <c r="D4" t="str">
-        <v>9786045678903</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>90000</v>
+        <v>9786045678902</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>79000</v>
       </c>
       <c r="G4" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="5">
@@ -499,19 +511,22 @@
         <v>2025-07-02 14:45:00</v>
       </c>
       <c r="C5" t="str">
-        <v>Cà Phê Cùng Tony - Bản Đặc Biệt</v>
+        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
       </c>
       <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
+        <v>9786045678903</v>
+      </c>
+      <c r="E5" t="str">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>95000</v>
+      <c r="F5" t="str">
+        <v>90000</v>
       </c>
       <c r="G5" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="6">
@@ -519,22 +534,25 @@
         <v>SP-20250703-01</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-07-03 08:10:00</v>
+        <v>2025-07-03 16:10:00</v>
       </c>
       <c r="C6" t="str">
-        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh (Bìa Mềm)</v>
+        <v>Cà Phê Cùng Tony - Bản Đẹp</v>
       </c>
       <c r="D6" t="str">
-        <v>9786045678905</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>hai</v>
-      </c>
-      <c r="F6">
-        <v>125000</v>
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>95000</v>
       </c>
       <c r="G6" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="7">
@@ -542,22 +560,25 @@
         <v>SP-20250703-02</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-07-03 16:00:00</v>
+        <v>2025-07-03 18:00:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Mắt Biếc (Bìa Mới)</v>
+        <v>Dế Mèn Phiêu Lưu Ký</v>
       </c>
       <c r="D7" t="str">
-        <v>9786045678906</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>110000</v>
+        <v>9786045678913</v>
+      </c>
+      <c r="E7" t="str">
+        <v>hai</v>
+      </c>
+      <c r="F7" t="str">
+        <v>55000</v>
       </c>
       <c r="G7" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="8">
@@ -565,22 +586,25 @@
         <v>SP-20250704-01</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-07-04 10:00:00</v>
+        <v>2025-07-04 09:15:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Khéo Ăn Nói Sẽ Có Được Thiên Hạ - Tập 1</v>
+        <v>Số Đỏ</v>
       </c>
       <c r="D8" t="str">
-        <v>9786045678907</v>
-      </c>
-      <c r="E8">
+        <v>9786045678910</v>
+      </c>
+      <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>110.000</v>
+        <v>35000</v>
       </c>
       <c r="G8" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="9">
@@ -588,22 +612,25 @@
         <v>SP-20250704-02</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-07-04 15:30:00</v>
+        <v>2025-07-04 14:30:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Đời Thay Đổi Khi Chúng Ta Thay Đổi (Bộ 1)</v>
+        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678908</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>75000</v>
+        <v>9786045678905</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>125000</v>
       </c>
       <c r="G9" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="10">
@@ -611,22 +638,25 @@
         <v>SP-20250705-01</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-07-05 11:15:00</v>
+        <v>2025-07-05 11:00:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Cha Giàu Cha Nghèo (Tập 1)</v>
+        <v>Sách Lập Trình React 19 Mới Nhất</v>
       </c>
       <c r="D10" t="str">
-        <v>9786045678909</v>
-      </c>
-      <c r="E10">
+        <v>9789999999999</v>
+      </c>
+      <c r="E10" t="str">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>135000</v>
+      <c r="F10" t="str">
+        <v>180000</v>
       </c>
       <c r="G10" t="str">
         <v>Shopee</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
     <row r="11">
@@ -634,372 +664,30 @@
         <v>SP-20250705-02</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-07-05 13:40:00</v>
+        <v>2025-07-05 16:45:00</v>
       </c>
       <c r="C11" t="str">
-        <v>Tư Duy Nhanh Và Chậm - Sách Tiếng Việt</v>
+        <v>Hạt Giống Tâm Hồn (Tập 1)</v>
       </c>
       <c r="D11" t="str">
-        <v>9786045678910</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>220000</v>
+        <v>9786045678918</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>75000</v>
       </c>
       <c r="G11" t="str">
         <v>Shopee</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>SP-20250706-01</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2025-07-06 09:50:00</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Người Giàu Có Nhất Thành Babylon (Bìa Cứng)</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>98000</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>SP-20250706-02</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2025-07-06 17:25:00</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Sức Mạnh Của Hiện Tại - Tái Bản 2025</v>
-      </c>
-      <c r="D13" t="str">
-        <v>9786045678912</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>130000</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>SP-20250707-01</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2025-07-07 10:05:00</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Lập Trình Node.js Từ Cơ Bản Đến Nâng Cao</v>
-      </c>
-      <c r="D14" t="str">
-        <v>9786049999999</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>180000</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>SP-20250707-02</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2025-07-07 14:15:00</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Đi Tìm Lẽ Sống (Bản Mới)</v>
-      </c>
-      <c r="D15" t="str">
-        <v>9786045678913</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>88000</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>SP-20250708-01</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2025-07-08 08:30:00</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Đọc Vị Bất Kỳ Ai - Tâm Lý Học ứng dụng</v>
-      </c>
-      <c r="D16" t="str">
-        <v>9786045678914</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>89000</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>SP-20250708-02</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2025-07-08 19:00:00</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Lược Sử Loài Người (Kèm Minh Họa)</v>
-      </c>
-      <c r="D17" t="str">
-        <v>9786045678915</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>240000</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>SP-20250709-01</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2025-07-09 12:20:00</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Hạt Giống Tâm Hồn - Tập 1</v>
-      </c>
-      <c r="D18" t="str">
-        <v>9786045678916</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>68000</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>SP-20250709-02</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2025-07-09 15:45:00</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Số Đỏ (Vũ Trọng Phụng)</v>
-      </c>
-      <c r="D19" t="str">
-        <v>9786045678917</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>65000</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>SP-20250710-01</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2025-07-10 10:10:00</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Tắt Đèn (Ngô Tất Tố)</v>
-      </c>
-      <c r="D20" t="str">
-        <v>9786045678918</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>55000</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>SP-20250710-02</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2025-07-10 16:50:00</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Rừng Na Uy - Haruki Murakami</v>
-      </c>
-      <c r="D21" t="str">
-        <v>9786045678919</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>145000</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>SP-20250711-01</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2025-07-11 09:00:00</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Thế Giới Quả Là Rộng Lớn Và Có Nhiều Việc Phải Làm - Daewoo</v>
-      </c>
-      <c r="D22" t="str">
-        <v>9786045678920</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>105000</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>SP-20250711-02</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2025-07-11 14:30:00</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Đắc Nhân Tâm - Dale Carnegie</v>
-      </c>
-      <c r="D23" t="str">
-        <v>9786045678901</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>86000</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>SP-20250712-01</v>
-      </c>
-      <c r="B24" t="str">
-        <v>2025-07-12 11:00:00</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Nhà Giả Kim - Paulo Coelho</v>
-      </c>
-      <c r="D24" t="str">
-        <v>9786045678902</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>79000</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>SP-20250712-02</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2025-07-12 17:15:00</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu - Rosie Nguyễn</v>
-      </c>
-      <c r="D25" t="str">
-        <v>9786045678903</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>90000</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Shopee</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>SP-20250713-01</v>
-      </c>
-      <c r="B26" t="str">
-        <v>2025-07-13 10:40:00</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Cha Giàu Cha Nghèo - Robert Kiyosaki</v>
-      </c>
-      <c r="D26" t="str">
-        <v>9786045678909</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>135000</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Shopee</v>
+      <c r="H11" t="str">
+        <v>Hoàn thành</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-online-shopee.xlsx
+++ b/sample-data/don-hang-online-shopee.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Đơn Shopee" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn Shopee Đa Ngành" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
         <v>2025-07-02 09:20:00</v>
       </c>
       <c r="C4" t="str">
-        <v>Nha Gia Kim</v>
+        <v>Nha Gia Kim (Bản tiếng Việt)</v>
       </c>
       <c r="D4" t="str">
         <v>9786045678902</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
         <v>79000</v>
@@ -511,16 +511,16 @@
         <v>2025-07-02 14:45:00</v>
       </c>
       <c r="C5" t="str">
-        <v>Tuổi Trẻ Đáng Giá Bao Nhiêu</v>
+        <v>Áo Thun Nam Cotton Coolmate (Trắng - Size L)</v>
       </c>
       <c r="D5" t="str">
-        <v>9786045678903</v>
+        <v>8935001234567</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>90000</v>
+        <v>199000</v>
       </c>
       <c r="G5" t="str">
         <v>Shopee</v>
@@ -537,16 +537,16 @@
         <v>2025-07-03 16:10:00</v>
       </c>
       <c r="C6" t="str">
-        <v>Cà Phê Cùng Tony - Bản Đẹp</v>
+        <v>Quần Jean Nam Slimfit Canifa (Xanh Đậm - 31)</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>8935001234568</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>95000</v>
+        <v>449000</v>
       </c>
       <c r="G6" t="str">
         <v>Shopee</v>
@@ -563,16 +563,16 @@
         <v>2025-07-03 18:00:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Dế Mèn Phiêu Lưu Ký</v>
+        <v>Giày Biti's Hunter Street - Đen 42</v>
       </c>
       <c r="D7" t="str">
-        <v>9786045678913</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>hai</v>
       </c>
       <c r="F7" t="str">
-        <v>55000</v>
+        <v>899000</v>
       </c>
       <c r="G7" t="str">
         <v>Shopee</v>
@@ -589,16 +589,16 @@
         <v>2025-07-04 09:15:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Số Đỏ</v>
+        <v>Nồi Chiên Không Dầu Philips 4.5L</v>
       </c>
       <c r="D8" t="str">
-        <v>9786045678910</v>
+        <v>8710103856789</v>
       </c>
       <c r="E8" t="str">
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>35000</v>
+        <v>1490000</v>
       </c>
       <c r="G8" t="str">
         <v>Shopee</v>
@@ -615,13 +615,13 @@
         <v>2025-07-04 14:30:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Tôi Thấy Hoa Vàng Trên Cỏ Xanh</v>
+        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678905</v>
+        <v>8935001234570</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
         <v>125000</v>
@@ -641,16 +641,16 @@
         <v>2025-07-05 11:00:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Sách Lập Trình React 19 Mới Nhất</v>
+        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
       </c>
       <c r="D10" t="str">
-        <v>9789999999999</v>
+        <v>6934177785678</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>180000</v>
+        <v>490000</v>
       </c>
       <c r="G10" t="str">
         <v>Shopee</v>
@@ -667,27 +667,79 @@
         <v>2025-07-05 16:45:00</v>
       </c>
       <c r="C11" t="str">
-        <v>Hạt Giống Tâm Hồn (Tập 1)</v>
+        <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
       </c>
       <c r="D11" t="str">
-        <v>9786045678918</v>
+        <v>3337875591079</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>75000</v>
+        <v>395000</v>
       </c>
       <c r="G11" t="str">
         <v>Shopee</v>
       </c>
       <c r="H11" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SP-20250706-01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-07-06 10:20:00</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Nước Tẩy Trang Bí Đao Cocoon</v>
+      </c>
+      <c r="D12" t="str">
+        <v>8936173200123</v>
+      </c>
+      <c r="E12" t="str">
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>245000</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SP-20250706-02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-07-06 15:10:00</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Sữa Rửa Mặt CeraVe Foaming Cleanser 236ml</v>
+      </c>
+      <c r="D13" t="str">
+        <v>3337875597354</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>320000</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H13" t="str">
         <v>Hoàn thành</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-online-shopee.xlsx
+++ b/sample-data/don-hang-online-shopee.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Đơn Shopee Đa Ngành" sheetId="1" r:id="rId1"/>
+    <sheet name="Đơn Shopee" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,13 +427,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SP-20250701-01</v>
+        <v>SP-20250701-001</v>
       </c>
       <c r="B2" t="str">
         <v>2025-07-01 10:15:00</v>
       </c>
       <c r="C2" t="str">
-        <v>Mãi mãi tuổi hai mươi</v>
+        <v>Mai mai tuoi hai muoi</v>
       </c>
       <c r="D2" t="str">
         <v>9786042392440</v>
@@ -453,13 +453,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SP-20250701-02</v>
+        <v>SP-20250701-002</v>
       </c>
       <c r="B3" t="str">
         <v>2025-07-01 11:30:00</v>
       </c>
       <c r="C3" t="str">
-        <v>Đắc Nhân Tâm</v>
+        <v>Dac Nhan Tam</v>
       </c>
       <c r="D3" t="str">
         <v>9786045678901</v>
@@ -479,13 +479,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SP-20250702-01</v>
+        <v>SP-20250701-003</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-07-02 09:20:00</v>
+        <v>2025-07-01 14:20:00</v>
       </c>
       <c r="C4" t="str">
-        <v>Nha Gia Kim (Bản tiếng Việt)</v>
+        <v>Nha Gia Kim (Ban tieng Viet)</v>
       </c>
       <c r="D4" t="str">
         <v>9786045678902</v>
@@ -505,22 +505,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SP-20250702-02</v>
+        <v>SP-20250702-001</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-07-02 14:45:00</v>
+        <v>2025-07-02 08:45:00</v>
       </c>
       <c r="C5" t="str">
-        <v>Áo Thun Nam Cotton Coolmate (Trắng - Size L)</v>
+        <v>Tuoi Tre Dang Gia Bao Nhieu</v>
       </c>
       <c r="D5" t="str">
-        <v>8935001234567</v>
+        <v>9786045678903</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>199000</v>
+        <v>90000</v>
       </c>
       <c r="G5" t="str">
         <v>Shopee</v>
@@ -531,22 +531,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SP-20250703-01</v>
+        <v>SP-20250702-002</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-07-03 16:10:00</v>
+        <v>2025-07-02 10:10:00</v>
       </c>
       <c r="C6" t="str">
-        <v>Quần Jean Nam Slimfit Canifa (Xanh Đậm - 31)</v>
+        <v>Ca Phe Cung Tony (Bia Mem)</v>
       </c>
       <c r="D6" t="str">
-        <v>8935001234568</v>
+        <v>9786045678904</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>449000</v>
+        <v>72000</v>
       </c>
       <c r="G6" t="str">
         <v>Shopee</v>
@@ -557,22 +557,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SP-20250703-02</v>
+        <v>SP-20250702-003</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-07-03 18:00:00</v>
+        <v>2025-07-02 13:25:00</v>
       </c>
       <c r="C7" t="str">
-        <v>Giày Biti's Hunter Street - Đen 42</v>
+        <v>Toi Thay Hoa Vang Tren Co Xanh</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>hai</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>899000</v>
+        <v>85000</v>
       </c>
       <c r="G7" t="str">
         <v>Shopee</v>
@@ -583,22 +583,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SP-20250704-01</v>
+        <v>SP-20250703-001</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-07-04 09:15:00</v>
+        <v>2025-07-03 09:00:00</v>
       </c>
       <c r="C8" t="str">
-        <v>Nồi Chiên Không Dầu Philips 4.5L</v>
+        <v>Cho Toi Xin Mot Ve Di Tuoi Tho</v>
       </c>
       <c r="D8" t="str">
-        <v>8710103856789</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>1490000</v>
+        <v>65000</v>
       </c>
       <c r="G8" t="str">
         <v>Shopee</v>
@@ -609,22 +609,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SP-20250704-02</v>
+        <v>SP-20250703-002</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-07-04 14:30:00</v>
+        <v>2025-07-03 11:30:00</v>
       </c>
       <c r="C9" t="str">
-        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
+        <v>Sapiens - Luoc Su Loai Nguoi</v>
       </c>
       <c r="D9" t="str">
-        <v>8935001234570</v>
+        <v>9786045678907</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>125000</v>
+        <v>189000</v>
       </c>
       <c r="G9" t="str">
         <v>Shopee</v>
@@ -635,22 +635,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SP-20250705-01</v>
+        <v>SP-20250703-003</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-07-05 11:00:00</v>
+        <v>2025-07-03 15:45:00</v>
       </c>
       <c r="C10" t="str">
-        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
+        <v>Atomic Habits</v>
       </c>
       <c r="D10" t="str">
-        <v>6934177785678</v>
+        <v>9786045678908</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>490000</v>
+        <v>149000</v>
       </c>
       <c r="G10" t="str">
         <v>Shopee</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SP-20250705-02</v>
+        <v>SP-20250704-001</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-07-05 16:45:00</v>
+        <v>2025-07-04 10:20:00</v>
       </c>
       <c r="C11" t="str">
-        <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
+        <v>Dam Bi Ghet</v>
       </c>
       <c r="D11" t="str">
-        <v>3337875591079</v>
+        <v>9786045678909</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>395000</v>
+        <v>115000</v>
       </c>
       <c r="G11" t="str">
         <v>Shopee</v>
@@ -687,22 +687,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SP-20250706-01</v>
+        <v>SP-20250704-002</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-07-06 10:20:00</v>
+        <v>2025-07-04 14:45:00</v>
       </c>
       <c r="C12" t="str">
-        <v>Nước Tẩy Trang Bí Đao Cocoon</v>
+        <v>Áo Thun Nam Cotton Coolmate (Trắng - Size L)</v>
       </c>
       <c r="D12" t="str">
-        <v>8936173200123</v>
+        <v>8935001234567</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>245000</v>
+        <v>199000</v>
       </c>
       <c r="G12" t="str">
         <v>Shopee</v>
@@ -713,33 +713,501 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SP-20250706-02</v>
+        <v>SP-20250705-001</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-07-06 15:10:00</v>
+        <v>2025-07-05 09:30:00</v>
       </c>
       <c r="C13" t="str">
+        <v>Quần Jean Nam Slimfit Canifa (Xanh Đậm - 31)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>8935001234568</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>449000</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SP-20250705-002</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-07-05 11:00:00</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Giày Biti's Hunter Street - Đen 42</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>hai</v>
+      </c>
+      <c r="F14" t="str">
+        <v>899000</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SP-20250705-003</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-07-05 16:20:00</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Áo Khoác Gió Uniqlo Chống Thấm</v>
+      </c>
+      <c r="D15" t="str">
+        <v>8935001234571</v>
+      </c>
+      <c r="E15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>550000</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SP-20250706-001</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-07-06 08:10:00</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Balo Laptop Tomtoc 15.6 inch Chống Sốc</v>
+      </c>
+      <c r="D16" t="str">
+        <v>8935001234573</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>890000</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SP-20250706-002</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-07-06 10:45:00</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Kinh Mat Phan Cuc Chong UV400 Rayban</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>1</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2490000</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SP-20250706-003</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-07-06 14:30:00</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dép Quai Ngang Adidas</v>
+      </c>
+      <c r="D18" t="str">
+        <v>8935001234575</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1</v>
+      </c>
+      <c r="F18" t="str">
+        <v>750000</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SP-20250707-001</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-07-07 09:15:00</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Non MLB NY Yankees</v>
+      </c>
+      <c r="D19" t="str">
+        <v>8935001234576</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1290000</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Shopee VN</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SP-20250707-002</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-07-07 11:00:00</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Nồi Chiên Không Dầu Philips 4.5L</v>
+      </c>
+      <c r="D20" t="str">
+        <v>8710103856789</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1490000</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SP-20250707-003</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-07-07 14:30:00</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
+      </c>
+      <c r="D21" t="str">
+        <v>8935001234570</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>125000</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SP-20250708-001</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-07-08 09:00:00</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
+      </c>
+      <c r="D22" t="str">
+        <v>6934177785678</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>490000</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SP-20250708-002</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-07-08 10:30:00</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Máy Xay Sinh Tố Lock&amp;Lock Cầm Tay</v>
+      </c>
+      <c r="D23" t="str">
+        <v>8935001234572</v>
+      </c>
+      <c r="E23" t="str">
+        <v>1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>550000</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SP-20250708-003</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-07-08 15:00:00</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
+      </c>
+      <c r="D24" t="str">
+        <v>3337875591079</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1</v>
+      </c>
+      <c r="F24" t="str">
+        <v>395000</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SP-20250709-001</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-07-09 08:40:00</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Nước Tẩy Trang Bí Đao Cocoon</v>
+      </c>
+      <c r="D25" t="str">
+        <v>8936173200123</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str">
+        <v>245000</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SP-20250709-002</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-07-09 12:15:00</v>
+      </c>
+      <c r="C26" t="str">
         <v>Sữa Rửa Mặt CeraVe Foaming Cleanser 236ml</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D26" t="str">
         <v>3337875597354</v>
       </c>
-      <c r="E13" t="str">
-        <v>1</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="E26" t="str">
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
         <v>320000</v>
       </c>
-      <c r="G13" t="str">
-        <v>Shopee</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Hoàn thành</v>
+      <c r="G26" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SP-20250709-003</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-07-09 17:30:00</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Đắc Nhân Tâm</v>
+      </c>
+      <c r="D27" t="str">
+        <v>9786045678901</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>86000</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Đã hủy</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SP-20250710-001</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-07-10 09:00:00</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Nhà Giả Kim</v>
+      </c>
+      <c r="D28" t="str">
+        <v>9786045678902</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>79000</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Trả hàng/Hoàn tiền</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SP-20250710-002</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-07-10 11:30:00</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Bình Giữ Nhiệt Inox 500ml Lock&amp;Lock</v>
+      </c>
+      <c r="D29" t="str">
+        <v>8935001299999</v>
+      </c>
+      <c r="E29" t="str">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>350000</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SP-20250710-003</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025-07-10 14:00:00</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Túi Tote Vải Canvas In Hình</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>89000</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Hoàn thành</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SP-20250701-001</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-07-01 10:16:00</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Mai mai tuoi hai muoi</v>
+      </c>
+      <c r="D31" t="str">
+        <v>9786042392440</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2</v>
+      </c>
+      <c r="F31" t="str">
+        <v>135000</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Shopee</v>
+      </c>
+      <c r="H31" t="str">
+        <v>giao thanh cong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-data/don-hang-online-shopee.xlsx
+++ b/sample-data/don-hang-online-shopee.xlsx
@@ -462,7 +462,7 @@
         <v>Dac Nhan Tam</v>
       </c>
       <c r="D3" t="str">
-        <v>9786045678901</v>
+        <v>9786045678909</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -488,7 +488,7 @@
         <v>Nha Gia Kim (Ban tieng Viet)</v>
       </c>
       <c r="D4" t="str">
-        <v>9786045678902</v>
+        <v>9786045678916</v>
       </c>
       <c r="E4" t="str">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>Tuoi Tre Dang Gia Bao Nhieu</v>
       </c>
       <c r="D5" t="str">
-        <v>9786045678903</v>
+        <v>9786045678923</v>
       </c>
       <c r="E5" t="str">
         <v>3</v>
@@ -540,7 +540,7 @@
         <v>Ca Phe Cung Tony (Bia Mem)</v>
       </c>
       <c r="D6" t="str">
-        <v>9786045678904</v>
+        <v>9786045678930</v>
       </c>
       <c r="E6" t="str">
         <v>1</v>
@@ -618,7 +618,7 @@
         <v>Sapiens - Luoc Su Loai Nguoi</v>
       </c>
       <c r="D9" t="str">
-        <v>9786045678907</v>
+        <v>9786045678961</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>Atomic Habits</v>
       </c>
       <c r="D10" t="str">
-        <v>9786045678908</v>
+        <v>9786045678978</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
@@ -670,7 +670,7 @@
         <v>Dam Bi Ghet</v>
       </c>
       <c r="D11" t="str">
-        <v>9786045678909</v>
+        <v>9786045678985</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>Áo Thun Nam Cotton Coolmate (Trắng - Size L)</v>
       </c>
       <c r="D12" t="str">
-        <v>8935001234567</v>
+        <v>8935001234562</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -722,7 +722,7 @@
         <v>Quần Jean Nam Slimfit Canifa (Xanh Đậm - 31)</v>
       </c>
       <c r="D13" t="str">
-        <v>8935001234568</v>
+        <v>8935001234579</v>
       </c>
       <c r="E13" t="str">
         <v>1</v>
@@ -774,7 +774,7 @@
         <v>Áo Khoác Gió Uniqlo Chống Thấm</v>
       </c>
       <c r="D15" t="str">
-        <v>8935001234571</v>
+        <v>8935001234593</v>
       </c>
       <c r="E15" t="str">
         <v>1</v>
@@ -800,7 +800,7 @@
         <v>Balo Laptop Tomtoc 15.6 inch Chống Sốc</v>
       </c>
       <c r="D16" t="str">
-        <v>8935001234573</v>
+        <v>8935001234609</v>
       </c>
       <c r="E16" t="str">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>Dép Quai Ngang Adidas</v>
       </c>
       <c r="D18" t="str">
-        <v>8935001234575</v>
+        <v>8935001234623</v>
       </c>
       <c r="E18" t="str">
         <v>1</v>
@@ -878,7 +878,7 @@
         <v>Non MLB NY Yankees</v>
       </c>
       <c r="D19" t="str">
-        <v>8935001234576</v>
+        <v>8935001234630</v>
       </c>
       <c r="E19" t="str">
         <v>1</v>
@@ -904,7 +904,7 @@
         <v>Nồi Chiên Không Dầu Philips 4.5L</v>
       </c>
       <c r="D20" t="str">
-        <v>8710103856789</v>
+        <v>8710103856788</v>
       </c>
       <c r="E20" t="str">
         <v>1</v>
@@ -930,7 +930,7 @@
         <v>Ấm Siêu Tốc Inox Sunhouse 1.8L</v>
       </c>
       <c r="D21" t="str">
-        <v>8935001234570</v>
+        <v>8935001234647</v>
       </c>
       <c r="E21" t="str">
         <v>2</v>
@@ -956,7 +956,7 @@
         <v>Tai Nghe Bluetooth Xiaomi Redmi Buds 4</v>
       </c>
       <c r="D22" t="str">
-        <v>6934177785678</v>
+        <v>6934177785672</v>
       </c>
       <c r="E22" t="str">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>Máy Xay Sinh Tố Lock&amp;Lock Cầm Tay</v>
       </c>
       <c r="D23" t="str">
-        <v>8935001234572</v>
+        <v>8935001234654</v>
       </c>
       <c r="E23" t="str">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>Kem Chống Nắng La Roche-Posay Anthelios</v>
       </c>
       <c r="D24" t="str">
-        <v>3337875591079</v>
+        <v>3337875591072</v>
       </c>
       <c r="E24" t="str">
         <v>1</v>
@@ -1034,7 +1034,7 @@
         <v>Nước Tẩy Trang Bí Đao Cocoon</v>
       </c>
       <c r="D25" t="str">
-        <v>8936173200123</v>
+        <v>8936173200126</v>
       </c>
       <c r="E25" t="str">
         <v>2</v>
@@ -1060,7 +1060,7 @@
         <v>Sữa Rửa Mặt CeraVe Foaming Cleanser 236ml</v>
       </c>
       <c r="D26" t="str">
-        <v>3337875597354</v>
+        <v>3337875597357</v>
       </c>
       <c r="E26" t="str">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>Đắc Nhân Tâm</v>
       </c>
       <c r="D27" t="str">
-        <v>9786045678901</v>
+        <v>9786045678909</v>
       </c>
       <c r="E27" t="str">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>Nhà Giả Kim</v>
       </c>
       <c r="D28" t="str">
-        <v>9786045678902</v>
+        <v>9786045678916</v>
       </c>
       <c r="E28" t="str">
         <v>2</v>
@@ -1138,7 +1138,7 @@
         <v>Bình Giữ Nhiệt Inox 500ml Lock&amp;Lock</v>
       </c>
       <c r="D29" t="str">
-        <v>8935001299999</v>
+        <v>8935001299990</v>
       </c>
       <c r="E29" t="str">
         <v>1</v>
